--- a/southern_europe/northern_italy_data/network_capex_metrics/capex_defined_per_arc.xlsx
+++ b/southern_europe/northern_italy_data/network_capex_metrics/capex_defined_per_arc.xlsx
@@ -483,7 +483,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>18166738.725</v>
+        <v>7957783.676</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -507,10 +507,10 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>19444629.66</v>
+        <v>8803569.749</v>
       </c>
       <c r="L2" t="n">
-        <v>32313290.356</v>
+        <v>15053969.292</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -527,13 +527,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>17669425.542</v>
+        <v>7957783.676</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>15408402.083</v>
+        <v>3966981.376</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -554,7 +554,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>18631289.868</v>
+        <v>4907439.29</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -577,16 +577,16 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>9816659.887</v>
+        <v>3966981.376</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>19922333.421</v>
+        <v>5443672.492</v>
       </c>
       <c r="F4" t="n">
-        <v>36150229.065</v>
+        <v>14971203.061</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -601,7 +601,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>15148553.733</v>
+        <v>4347955.574</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -627,13 +627,13 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>14507913.023</v>
+        <v>5443672.492</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>35447970.195</v>
+        <v>12109847.591</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -651,7 +651,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>40459189.958</v>
+        <v>14107846.7</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -683,7 +683,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>14132609.154</v>
+        <v>3089585.036</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -698,7 +698,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>31613557.759</v>
+        <v>12566007.576</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -727,7 +727,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>10703491.567</v>
+        <v>3089585.036</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -736,10 +736,10 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>53252000.454</v>
+        <v>22903305.32</v>
       </c>
       <c r="J7" t="n">
-        <v>60129598.039</v>
+        <v>26718594.952</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -786,13 +786,13 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>65486971.682</v>
+        <v>24938086.683</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>22155800.104</v>
+        <v>7187542.885</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -833,7 +833,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>16104871.059</v>
+        <v>8618455.384</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -842,10 +842,10 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>26927172.167</v>
+        <v>13948983.432</v>
       </c>
       <c r="N9" t="n">
-        <v>24834690.143</v>
+        <v>12604159.2</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>18334544.95</v>
+        <v>8618455.384</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -889,10 +889,10 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>28595190.032</v>
+        <v>12498016.705</v>
       </c>
       <c r="N10" t="n">
-        <v>26337932.373</v>
+        <v>13372445.895</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -915,7 +915,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>33705480.636</v>
+        <v>14276197.316</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -933,7 +933,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>21945871.287</v>
+        <v>10083599.51</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -962,7 +962,7 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>22766658.805</v>
+        <v>12566007.576</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -971,10 +971,10 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>52272157.247</v>
+        <v>28314023.447</v>
       </c>
       <c r="J12" t="n">
-        <v>58618840.823</v>
+        <v>28049463.998</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1033,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>12608848.441</v>
+        <v>4471489.716</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1083,7 +1083,7 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>11884573.114</v>
+        <v>2957001.94</v>
       </c>
     </row>
     <row r="15">
@@ -1199,7 +1199,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>84104.223</v>
+        <v>167761.049</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -1223,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>86460.64999999999</v>
+        <v>187139.234</v>
       </c>
       <c r="L2" t="n">
-        <v>122518.458</v>
+        <v>273249.781</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -1243,13 +1243,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>73720.255</v>
+        <v>167761.049</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>66355.183</v>
+        <v>141121.707</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>69670.851</v>
+        <v>157246.934</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1293,16 +1293,16 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>61761.846</v>
+        <v>141121.707</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>81387.25599999999</v>
+        <v>160620.742</v>
       </c>
       <c r="F4" t="n">
-        <v>126662.719</v>
+        <v>271218.646</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -1317,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>72145.337</v>
+        <v>146995.013</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1343,13 +1343,13 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>64331.355</v>
+        <v>160620.742</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>103970.99</v>
+        <v>249211.176</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -1367,7 +1367,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>114880.037</v>
+        <v>281916.967</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -1399,7 +1399,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>61538.278</v>
+        <v>136220.409</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1414,7 +1414,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>103928.904</v>
+        <v>266175.839</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1443,7 +1443,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>53977.002</v>
+        <v>136220.409</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1452,10 +1452,10 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>150290.554</v>
+        <v>391772.249</v>
       </c>
       <c r="J7" t="n">
-        <v>167383.065</v>
+        <v>437766.201</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1502,13 +1502,13 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>170281.957</v>
+        <v>425280.658</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>81174.67600000001</v>
+        <v>162533.559</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1549,7 +1549,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>84628.508</v>
+        <v>184618.539</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1558,10 +1558,10 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>119579.679</v>
+        <v>279433.566</v>
       </c>
       <c r="N9" t="n">
-        <v>113233.248</v>
+        <v>266376.915</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1593,7 +1593,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>89919.15300000001</v>
+        <v>184618.539</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1605,10 +1605,10 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>112269.182</v>
+        <v>256198.589</v>
       </c>
       <c r="N10" t="n">
-        <v>115590.308</v>
+        <v>262914.181</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1631,7 +1631,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>128204.395</v>
+        <v>278519.789</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1649,7 +1649,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>97824.55100000001</v>
+        <v>211382.582</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1678,7 +1678,7 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>105965.712</v>
+        <v>266175.839</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1687,10 +1687,10 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>194662.366</v>
+        <v>460386.765</v>
       </c>
       <c r="J12" t="n">
-        <v>195873.188</v>
+        <v>456323.81</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1749,7 +1749,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>66147.799</v>
+        <v>148732.593</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>77356.432</v>
+        <v>210083.199</v>
       </c>
     </row>
     <row r="15">

--- a/southern_europe/northern_italy_data/network_capex_metrics/capex_defined_per_arc.xlsx
+++ b/southern_europe/northern_italy_data/network_capex_metrics/capex_defined_per_arc.xlsx
@@ -483,7 +483,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>7957783.676</v>
+        <v>6695528.215</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -507,10 +507,10 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>8803569.749</v>
+        <v>7208022.944</v>
       </c>
       <c r="L2" t="n">
-        <v>15053969.292</v>
+        <v>14157854.801</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -527,13 +527,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>7957783.676</v>
+        <v>6695528.215</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>3966981.376</v>
+        <v>2864092.355</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -554,7 +554,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>4907439.29</v>
+        <v>3860381.143</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -577,16 +577,16 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>3966981.376</v>
+        <v>2864092.355</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>5443672.492</v>
+        <v>4372887.984</v>
       </c>
       <c r="F4" t="n">
-        <v>14971203.061</v>
+        <v>14054089.195</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -601,7 +601,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>4347955.574</v>
+        <v>3261728.69</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -627,13 +627,13 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>5443672.492</v>
+        <v>4372887.984</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>12109847.591</v>
+        <v>11241650.264</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -651,7 +651,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>14107846.7</v>
+        <v>13544461.586</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -683,7 +683,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>3089585.036</v>
+        <v>1931648.341</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -698,7 +698,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>12566007.576</v>
+        <v>11738115.476</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -727,7 +727,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>3089585.036</v>
+        <v>1931648.341</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -736,10 +736,10 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>22903305.32</v>
+        <v>21966233.117</v>
       </c>
       <c r="J7" t="n">
-        <v>26718594.952</v>
+        <v>26211268.648</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -786,13 +786,13 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>24938086.683</v>
+        <v>24555522.842</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>7187542.885</v>
+        <v>5748933.704</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -833,7 +833,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>8618455.384</v>
+        <v>7397819.384</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -842,10 +842,10 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>13948983.432</v>
+        <v>13437165.081</v>
       </c>
       <c r="N9" t="n">
-        <v>12604159.2</v>
+        <v>11777573.449</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>8618455.384</v>
+        <v>7397819.384</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -889,10 +889,10 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>12498016.705</v>
+        <v>11481342.749</v>
       </c>
       <c r="N10" t="n">
-        <v>13372445.895</v>
+        <v>12235677.164</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -915,7 +915,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>14276197.316</v>
+        <v>13656540.457</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -933,7 +933,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>10083599.51</v>
+        <v>8828765.334000001</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -962,7 +962,7 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>12566007.576</v>
+        <v>11738115.476</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -971,10 +971,10 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>28314023.447</v>
+        <v>27673949.632</v>
       </c>
       <c r="J12" t="n">
-        <v>28049463.998</v>
+        <v>27396516.471</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1033,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>4471489.716</v>
+        <v>3402136.127</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1083,7 +1083,7 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2957001.94</v>
+        <v>2566575.505</v>
       </c>
     </row>
     <row r="15">
@@ -1199,7 +1199,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>167761.049</v>
+        <v>86581.04700000001</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -1223,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>187139.234</v>
+        <v>114086.215</v>
       </c>
       <c r="L2" t="n">
-        <v>273249.781</v>
+        <v>183644.247</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -1243,13 +1243,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>167761.049</v>
+        <v>86581.04700000001</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>141121.707</v>
+        <v>38300.709</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>157246.934</v>
+        <v>58138.338</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1293,16 +1293,16 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>141121.707</v>
+        <v>38300.709</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>160620.742</v>
+        <v>66128.685</v>
       </c>
       <c r="F4" t="n">
-        <v>271218.646</v>
+        <v>182511.905</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -1317,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>146995.013</v>
+        <v>46407.396</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1343,13 +1343,13 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>160620.742</v>
+        <v>66128.685</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>249211.176</v>
+        <v>151660.215</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -1367,7 +1367,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>281916.967</v>
+        <v>177060.39</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -1399,7 +1399,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>136220.409</v>
+        <v>32801.604</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1414,7 +1414,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>266175.839</v>
+        <v>167477.521</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1443,7 +1443,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>136220.409</v>
+        <v>32801.604</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1452,10 +1452,10 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>391772.249</v>
+        <v>315082.037</v>
       </c>
       <c r="J7" t="n">
-        <v>437766.201</v>
+        <v>356577.263</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1502,13 +1502,13 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>425280.658</v>
+        <v>331014.651</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>162533.559</v>
+        <v>84069.281</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1549,7 +1549,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>184618.539</v>
+        <v>103374.092</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1558,10 +1558,10 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>279433.566</v>
+        <v>173954.129</v>
       </c>
       <c r="N9" t="n">
-        <v>266376.915</v>
+        <v>168004.829</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1593,7 +1593,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>184618.539</v>
+        <v>103374.092</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1605,10 +1605,10 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>256198.589</v>
+        <v>166048.554</v>
       </c>
       <c r="N10" t="n">
-        <v>262914.181</v>
+        <v>175083.568</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1631,7 +1631,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>278519.789</v>
+        <v>178349.043</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1649,7 +1649,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>211382.582</v>
+        <v>126408.884</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1678,7 +1678,7 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>266175.839</v>
+        <v>167477.521</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1687,10 +1687,10 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>460386.765</v>
+        <v>383502.913</v>
       </c>
       <c r="J12" t="n">
-        <v>456323.81</v>
+        <v>380153.046</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1749,7 +1749,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>148732.593</v>
+        <v>48034.336</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>210083.199</v>
+        <v>81770.235</v>
       </c>
     </row>
     <row r="15">
